--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487672_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487672_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MENDOZA ALVAREZ</t>
+          <t>J. MUNRO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5204</v>
+        <v>3.1788</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3331</v>
+        <v>4.328</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1873</v>
+        <v>-1.1492</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.1818</v>
+        <v>3.3327</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.4566</v>
+        <v>2.9906</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7252</v>
+        <v>0.342</v>
       </c>
       <c r="J2" t="n">
-        <v>-3.6097</v>
+        <v>4.3922</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.6889</v>
+        <v>3.2049</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.9208</v>
+        <v>1.1874</v>
       </c>
       <c r="M2" t="n">
-        <v>1.4279</v>
+        <v>-1.0596</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2323</v>
+        <v>-0.2142</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1956</v>
+        <v>-0.8454</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1344</v>
+        <v>-0.3881</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1783</v>
+        <v>-0.0541</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2772</v>
+        <v>0.0417</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9011</v>
+        <v>-0.0959</v>
       </c>
       <c r="V2" t="n">
-        <v>4.688</v>
+        <v>-0.8758</v>
       </c>
       <c r="W2" t="n">
-        <v>4.7999</v>
+        <v>0.2821</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1119</v>
+        <v>-1.1579</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MUNRO</t>
+          <t>J. MENDOZA ALVAREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7789</v>
+        <v>2.4911</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2279</v>
+        <v>-0.0693</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.449</v>
+        <v>2.5604</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3327</v>
+        <v>-2.1818</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9906</v>
+        <v>-1.4566</v>
       </c>
       <c r="I3" t="n">
-        <v>0.342</v>
+        <v>-0.7252</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3922</v>
+        <v>-3.6097</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2049</v>
+        <v>-1.6889</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1874</v>
+        <v>-1.9208</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0596</v>
+        <v>1.4279</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2142</v>
+        <v>0.2323</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8454</v>
+        <v>1.1956</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7761</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.3881</v>
+        <v>-2.1344</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.454</v>
+        <v>1.1491</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0584</v>
+        <v>0.8748</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3957</v>
+        <v>0.2743</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.8758</v>
+        <v>4.688</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2821</v>
+        <v>4.7999</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1579</v>
+        <v>-0.1119</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1641</v>
+        <v>0.5189</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1605</v>
+        <v>0.1398</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3246</v>
+        <v>0.3791</v>
       </c>
       <c r="G4" t="n">
         <v>0.5432</v>
@@ -766,13 +766,13 @@
         <v>0.194</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2059</v>
+        <v>0.1489</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2423</v>
+        <v>0.058</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3672</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PRATS PEINADO</t>
+          <t>E. ECHEVERRIA MATEO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4311</v>
+        <v>-0.0789</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.4959</v>
+        <v>0.4737</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0648</v>
+        <v>-0.5526</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1625</v>
+        <v>-1.3467</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8716</v>
+        <v>-1.2366</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2908</v>
+        <v>-0.1101</v>
       </c>
       <c r="J5" t="n">
-        <v>0.123</v>
+        <v>0.0731</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0824</v>
+        <v>-1.1905</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0406</v>
+        <v>1.2635</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0395</v>
+        <v>-1.4198</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7893</v>
+        <v>-0.0462</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2502</v>
+        <v>-1.3737</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1344</v>
+        <v>-1.1642</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2189</v>
+        <v>0.2944</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4845</v>
+        <v>0.3409</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2656</v>
+        <v>-0.0465</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.4045</v>
+        <v>1.1675</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4045</v>
+        <v>-0.0564</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. ECHEVERRIA MATEO</t>
+          <t>J. PRATS PEINADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6701</v>
+        <v>-0.1942</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0733</v>
+        <v>-2.0955</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7433999999999999</v>
+        <v>1.9013</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3467</v>
+        <v>1.1625</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2366</v>
+        <v>0.8716</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1101</v>
+        <v>0.2908</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0731</v>
+        <v>0.123</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1905</v>
+        <v>0.0824</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2635</v>
+        <v>0.0406</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4198</v>
+        <v>1.0395</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0462</v>
+        <v>0.7893</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3737</v>
+        <v>0.2502</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1642</v>
+        <v>-2.1344</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2968</v>
+        <v>0.0179</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0595</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2373</v>
+        <v>0.1021</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1675</v>
+        <v>-0.4045</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0564</v>
+        <v>-0.4045</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BARRA DE LA CRUZ</t>
+          <t>G. HIERRO ABAD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.6073</v>
+        <v>-2.2086</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1672</v>
+        <v>-4.0202</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.44</v>
+        <v>1.8117</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.2921</v>
+        <v>0.0389</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9641</v>
+        <v>0.2875</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.328</v>
+        <v>-0.2486</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.4671</v>
+        <v>-0.911</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.8454</v>
+        <v>-0.2842</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6217</v>
+        <v>-0.6267</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.825</v>
+        <v>0.9499</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1187</v>
+        <v>0.5718</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7063</v>
+        <v>0.3781</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3582</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.194</v>
+        <v>-3.1045</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5523</v>
+        <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1278</v>
+        <v>-0.4669</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3656</v>
+        <v>-0.2869</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2378</v>
+        <v>-0.18</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8012</v>
+        <v>0.1597</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1283</v>
+        <v>0.2821</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.9295</v>
+        <v>-0.1224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. HIERRO ABAD</t>
+          <t>J. BARRA DE LA CRUZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8998</v>
+        <v>-2.2708</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.5207</v>
+        <v>-0.967</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6209</v>
+        <v>-1.3037</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0389</v>
+        <v>-3.2921</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2875</v>
+        <v>-1.9641</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2486</v>
+        <v>-1.328</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.911</v>
+        <v>-2.4671</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2842</v>
+        <v>-1.8454</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6267</v>
+        <v>-0.6217</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9499</v>
+        <v>-0.825</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5718</v>
+        <v>-0.1187</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3781</v>
+        <v>-0.7063</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.9403</v>
+        <v>1.3582</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1045</v>
+        <v>-0.194</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1581</v>
+        <v>0.4643</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7874</v>
+        <v>0.5658</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3708</v>
+        <v>-0.1015</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1597</v>
+        <v>-0.8012</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2821</v>
+        <v>1.1283</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1224</v>
+        <v>-1.9295</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>A. DE LAS HERAS SANZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9039</v>
+        <v>-2.4355</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.27</v>
+        <v>-2.0458</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3661</v>
+        <v>-0.3897</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1043</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3123</v>
+        <v>-1.2234</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4166</v>
+        <v>0.6151</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5872000000000001</v>
+        <v>-1.1917</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5644</v>
+        <v>-1.2729</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0228</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6915</v>
+        <v>0.5833</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2521</v>
+        <v>0.0494</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4394</v>
+        <v>0.5339</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.9403</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1045</v>
+        <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1642</v>
+        <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0538</v>
+        <v>0.346</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4229</v>
+        <v>0.1161</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4767</v>
+        <v>0.2299</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9131</v>
+        <v>-1.591</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5833</v>
+        <v>-1.591</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. DE LAS HERAS SANZ</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2542</v>
+        <v>-3.3127</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6464</v>
+        <v>-3.27</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6078</v>
+        <v>-0.0427</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.1043</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2234</v>
+        <v>0.3123</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6151</v>
+        <v>-0.4166</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1917</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2729</v>
+        <v>0.5644</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0228</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5833</v>
+        <v>-0.6915</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0494</v>
+        <v>-0.2521</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5339</v>
+        <v>-0.4394</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5821</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9702</v>
+        <v>-3.1045</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4726</v>
+        <v>-0.355</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4845</v>
+        <v>-0.4229</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0119</v>
+        <v>0.0679</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.591</v>
+        <v>-0.9131</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.591</v>
+        <v>-0.5833</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0865</v>
+        <v>-4.2778</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.729</v>
+        <v>-1.0293</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3575</v>
+        <v>-3.2485</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9346</v>
@@ -1312,13 +1312,13 @@
         <v>0.5821</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1702</v>
+        <v>-0.021</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4262</v>
+        <v>0.1259</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2559</v>
+        <v>-0.1469</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7698</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0501</v>
+        <v>-4.8499</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.7614</v>
+        <v>-4.5612</v>
       </c>
       <c r="F12" t="n">
         <v>-0.2887</v>
@@ -1390,10 +1390,10 @@
         <v>0.3881</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3275</v>
+        <v>-0.1273</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3634</v>
+        <v>-0.1632</v>
       </c>
       <c r="U12" t="n">
         <v>0.0359</v>
@@ -1429,16 +1429,16 @@
         <v>-13.1168</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3226999999999998</v>
+        <v>-0.3226000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-4.1729</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.394299999999999</v>
+        <v>-3.3943</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.7787000000000002</v>
       </c>
       <c r="J13" t="n">
         <v>-3.518599999999999</v>
@@ -1447,10 +1447,10 @@
         <v>-4.3251</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8065999999999998</v>
+        <v>0.8065999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6543999999999995</v>
+        <v>-0.6544</v>
       </c>
       <c r="N13" t="n">
         <v>0.9308</v>
@@ -1471,16 +1471,16 @@
         <v>1.3963</v>
       </c>
       <c r="T13" t="n">
-        <v>1.166100000000001</v>
+        <v>1.1661</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2300000000000001</v>
+        <v>0.2301</v>
       </c>
       <c r="V13" t="n">
         <v>-1.9313</v>
       </c>
       <c r="W13" t="n">
-        <v>7.6685</v>
+        <v>7.668499999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-9.599900000000002</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.5002</v>
+        <v>11.0448</v>
       </c>
       <c r="E14" t="n">
-        <v>7.4357</v>
+        <v>5.9342</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0645</v>
+        <v>5.1106</v>
       </c>
       <c r="G14" t="n">
         <v>5.5835</v>
@@ -1546,13 +1546,13 @@
         <v>3.4926</v>
       </c>
       <c r="S14" t="n">
-        <v>3.8493</v>
+        <v>1.3938</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1859</v>
+        <v>0.6844</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6634</v>
+        <v>0.7094</v>
       </c>
       <c r="V14" t="n">
         <v>1.5451</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7408</v>
+        <v>5.3136</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3686</v>
+        <v>3.6689</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3722</v>
+        <v>1.6447</v>
       </c>
       <c r="G15" t="n">
         <v>4.0234</v>
@@ -1624,13 +1624,13 @@
         <v>2.3284</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2546</v>
+        <v>0.3182</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2412</v>
+        <v>0.0591</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0134</v>
+        <v>0.2591</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3863</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1916</v>
+        <v>4.4965</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9253</v>
+        <v>2.1181</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2664</v>
+        <v>2.3784</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6242</v>
+        <v>2.4418</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4325</v>
+        <v>2.4996</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1917</v>
+        <v>-0.0578</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6023</v>
+        <v>1.3417</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3336</v>
+        <v>1.9279</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9359</v>
+        <v>-0.5861</v>
       </c>
       <c r="M16" t="n">
-        <v>1.022</v>
+        <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7662</v>
+        <v>0.5718</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2558</v>
+        <v>0.5283</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2669</v>
+        <v>-0.5187</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2412</v>
+        <v>-0.4475</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0258</v>
+        <v>-0.0712</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2821</v>
+        <v>1.2152</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5642</v>
+        <v>1.2239</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2821</v>
+        <v>-0.0086</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.1234</v>
+        <v>4.1916</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7177</v>
+        <v>1.9253</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4057</v>
+        <v>2.2664</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4418</v>
+        <v>2.6242</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4996</v>
+        <v>0.4325</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0578</v>
+        <v>2.1917</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3417</v>
+        <v>1.6023</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9279</v>
+        <v>-0.3336</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5861</v>
+        <v>1.9359</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>1.022</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5718</v>
+        <v>0.7662</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5283</v>
+        <v>0.2558</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8919</v>
+        <v>-0.2669</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8479</v>
+        <v>-0.2412</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0439</v>
+        <v>-0.0258</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2152</v>
+        <v>0.2821</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2239</v>
+        <v>0.5642</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.0086</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0117</v>
+        <v>1.7476</v>
       </c>
       <c r="E18" t="n">
-        <v>3.5917</v>
+        <v>3.1913</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.58</v>
+        <v>-1.4437</v>
       </c>
       <c r="G18" t="n">
         <v>1.4624</v>
@@ -1858,13 +1858,13 @@
         <v>2.3284</v>
       </c>
       <c r="S18" t="n">
-        <v>0.443</v>
+        <v>0.1789</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8501</v>
+        <v>0.4497</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4071</v>
+        <v>-0.2708</v>
       </c>
       <c r="V18" t="n">
         <v>-2.2221</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0538</v>
+        <v>0.1084</v>
       </c>
       <c r="E19" t="n">
         <v>-0.116</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1698</v>
+        <v>0.2243</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5339</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0242</v>
+        <v>0.0303</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>0.6119</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6415</v>
+        <v>-0.305</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6435</v>
+        <v>-1.4433</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0021</v>
+        <v>1.1384</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2448</v>
@@ -2014,13 +2014,13 @@
         <v>2.7164</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3701</v>
+        <v>-0.0336</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0011</v>
+        <v>0.2013</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3712</v>
+        <v>-0.2349</v>
       </c>
       <c r="V20" t="n">
         <v>1.1675</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5871</v>
+        <v>-2.0504</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5187</v>
+        <v>-2.1183</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0684</v>
+        <v>0.0679</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6344</v>
@@ -2092,13 +2092,13 @@
         <v>1.3582</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8064</v>
+        <v>-0.2697</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6662</v>
+        <v>-0.2658</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1402</v>
+        <v>-0.0039</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5642</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>H. PEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1205</v>
+        <v>-2.988</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4453</v>
+        <v>-3.6806</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6751</v>
+        <v>0.6926</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.3229</v>
+        <v>-3.5732</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0448</v>
+        <v>-2.8769</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2781</v>
+        <v>-0.6963</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.9608</v>
+        <v>-3.9394</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.9608</v>
+        <v>-3.2543</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-0.6851</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3621</v>
+        <v>0.3662</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0.3773</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2781</v>
+        <v>-0.0111</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9035</v>
+        <v>-1.0551</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4845</v>
+        <v>-0.3054</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.419</v>
+        <v>-0.7498</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2821</v>
+        <v>0.2821</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X22" t="n">
         <v>-0.2821</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H. PEREZ SANCHEZ</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4791</v>
+        <v>-3.002</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.9809</v>
+        <v>-2.2451</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5018</v>
+        <v>-0.7569</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.5732</v>
+        <v>-2.3229</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8769</v>
+        <v>-2.0448</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6963</v>
+        <v>-0.2781</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.9394</v>
+        <v>-1.9608</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.2543</v>
+        <v>-1.9608</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6851</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3662</v>
+        <v>-0.3621</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3773</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0111</v>
+        <v>-0.2781</v>
       </c>
       <c r="P23" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5462</v>
+        <v>-0.7851</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6057</v>
+        <v>-0.2843</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9405</v>
+        <v>-0.5008</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2821</v>
+        <v>-0.2821</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>-0.2821</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.354</v>
+        <v>-5.1176</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.012</v>
+        <v>-6.9119</v>
       </c>
       <c r="F24" t="n">
-        <v>1.658</v>
+        <v>1.7943</v>
       </c>
       <c r="G24" t="n">
         <v>-3.6531</v>
@@ -2326,13 +2326,13 @@
         <v>1.5523</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6247</v>
+        <v>-0.3883</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.12</v>
+        <v>-0.0199</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5047</v>
+        <v>-0.3684</v>
       </c>
       <c r="V24" t="n">
         <v>0.2821</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>13.4393</v>
+        <v>13.4395</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3225999999999987</v>
+        <v>0.3225999999999996</v>
       </c>
       <c r="F25" t="n">
         <v>13.117</v>
@@ -2371,16 +2371,16 @@
         <v>4.173</v>
       </c>
       <c r="H25" t="n">
-        <v>3.3944</v>
+        <v>3.394400000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7787000000000004</v>
+        <v>0.7787000000000006</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6545000000000005</v>
+        <v>0.6545000000000014</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.9308999999999998</v>
+        <v>-0.9309000000000003</v>
       </c>
       <c r="L25" t="n">
         <v>1.585300000000001</v>
@@ -2410,7 +2410,7 @@
         <v>-0.2301999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.1661</v>
+        <v>-1.1663</v>
       </c>
       <c r="V25" t="n">
         <v>1.9313</v>
